--- a/Formatos/Visita 2 GFPI-F023.xlsx
+++ b/Formatos/Visita 2 GFPI-F023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SEANT\OneDrive\Documents\Seto 2026\sena\Manual SENA Etapa Productiva\manual-general-aprendiz\Formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB96AD8-3DCC-4223-BE1E-450E2E7502C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDF30C7-26BD-48D7-9F45-EB6435A6BDC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{BC3553EE-4E49-4F2A-B03E-CFAC4EB3009B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t>Información general</t>
   </si>
@@ -117,12 +117,6 @@
   </si>
   <si>
     <t>Nombre:</t>
-  </si>
-  <si>
-    <t>Sergio Andrés Torres Martínez</t>
-  </si>
-  <si>
-    <t>satorres@sena.edu.co</t>
   </si>
   <si>
     <t xml:space="preserve">Datos del ente co-formador </t>
@@ -785,7 +779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -833,6 +827,383 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="justify" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -863,18 +1234,9 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -896,30 +1258,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -948,364 +1286,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -1323,7 +1309,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1741,6 +1727,7 @@
     <col min="11" max="11" width="7.5703125" customWidth="1"/>
     <col min="12" max="12" width="3.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="15" width="0" hidden="1" customWidth="1"/>
     <col min="16" max="16384" width="11.42578125" hidden="1"/>
   </cols>
   <sheetData>
@@ -1760,1003 +1747,999 @@
       <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
     </row>
     <row r="3" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="53" t="s">
+      <c r="B3" s="82"/>
+      <c r="C3" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="55"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="100"/>
     </row>
     <row r="4" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="87" t="s">
+      <c r="B4" s="82"/>
+      <c r="C4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="89"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
       <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="21"/>
+      <c r="I4" s="132"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="134"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="100" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="101"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="63"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="119"/>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="55"/>
-      <c r="F6" s="102" t="s">
+      <c r="E6" s="100"/>
+      <c r="F6" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="103"/>
+      <c r="G6" s="42"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="102" t="s">
+      <c r="I6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="103"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="66"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="122"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="91"/>
-      <c r="E7" s="91"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="90" t="s">
+      <c r="B7" s="82"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="91"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="63"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="119"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="93" t="s">
+      <c r="A8" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="60"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="106"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="72"/>
-      <c r="B9" s="94" t="s">
+      <c r="A9" s="90"/>
+      <c r="B9" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="95"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="69"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="123"/>
+      <c r="F9" s="124"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="124"/>
+      <c r="K9" s="124"/>
+      <c r="L9" s="124"/>
+      <c r="M9" s="125"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="72"/>
-      <c r="B10" s="35" t="s">
+      <c r="A10" s="90"/>
+      <c r="B10" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="59"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="59"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="60"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="105"/>
+      <c r="G10" s="105"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="105"/>
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="106"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="72"/>
-      <c r="B11" s="35" t="s">
+      <c r="A11" s="90"/>
+      <c r="B11" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="60"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="105"/>
+      <c r="I11" s="105"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="106"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="72"/>
-      <c r="B12" s="35" t="s">
+      <c r="A12" s="90"/>
+      <c r="B12" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="59"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="59"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="60"/>
+      <c r="C12" s="92"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="106"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="72"/>
-      <c r="B13" s="35" t="s">
+      <c r="A13" s="90"/>
+      <c r="B13" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="60"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="105"/>
+      <c r="M13" s="106"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="72"/>
-      <c r="B14" s="35" t="s">
+      <c r="A14" s="90"/>
+      <c r="B14" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="41"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="101"/>
+      <c r="F14" s="102"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="103"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="72"/>
-      <c r="B15" s="35" t="s">
+      <c r="A15" s="90"/>
+      <c r="B15" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="41"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="103"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="73"/>
-      <c r="B16" s="35" t="s">
+      <c r="A16" s="91"/>
+      <c r="B16" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="101"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="102"/>
+      <c r="K16" s="102"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="103"/>
     </row>
     <row r="17" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
-      <c r="J17" s="75"/>
-      <c r="K17" s="75"/>
-      <c r="L17" s="75"/>
-      <c r="M17" s="76"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="109"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="109"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="109"/>
+      <c r="M17" s="110"/>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="72"/>
-      <c r="B18" s="35" t="s">
+      <c r="A18" s="90"/>
+      <c r="B18" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="79"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="82"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="70"/>
+      <c r="M18" s="71"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="73"/>
-      <c r="B19" s="35" t="s">
+      <c r="A19" s="91"/>
+      <c r="B19" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
-      <c r="J19" s="75"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="75"/>
-      <c r="M19" s="76"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="82"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="109"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="110"/>
     </row>
     <row r="20" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="60"/>
+        <v>27</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="92"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="106"/>
     </row>
     <row r="21" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="60"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="106"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="60"/>
+      <c r="B22" s="81" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="92"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="105"/>
+      <c r="M22" s="106"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="60"/>
+      <c r="B23" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="92"/>
+      <c r="D23" s="82"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="106"/>
     </row>
     <row r="24" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="52"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="60"/>
+        <v>29</v>
+      </c>
+      <c r="B24" s="81" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="92"/>
+      <c r="D24" s="82"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="106"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
-      <c r="B25" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="52"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="60"/>
+      <c r="B25" s="81" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="92"/>
+      <c r="D25" s="82"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="106"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="41"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="82"/>
+      <c r="E26" s="101"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
+      <c r="I26" s="102"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="102"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="103"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
-      <c r="B27" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="52"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="60"/>
+      <c r="B27" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="92"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="106"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
-      <c r="B28" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="41"/>
+      <c r="B28" s="126" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="127"/>
+      <c r="D28" s="128"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="102"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="103"/>
     </row>
     <row r="29" spans="1:13" ht="25.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="41"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="101"/>
+      <c r="F29" s="102"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="102"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="103"/>
     </row>
     <row r="30" spans="1:13" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="52"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="41"/>
+      <c r="C30" s="92"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="101"/>
+      <c r="F30" s="102"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="102"/>
+      <c r="I30" s="102"/>
+      <c r="J30" s="102"/>
+      <c r="K30" s="102"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="103"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
-      <c r="B31" s="35" t="s">
+      <c r="B31" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="52"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="40"/>
-      <c r="M31" s="41"/>
+      <c r="C31" s="92"/>
+      <c r="D31" s="82"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="102"/>
+      <c r="I31" s="102"/>
+      <c r="J31" s="102"/>
+      <c r="K31" s="102"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="103"/>
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
+      <c r="A32" s="130" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="130"/>
+      <c r="C32" s="130"/>
+      <c r="D32" s="130"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="130"/>
+      <c r="H32" s="130"/>
+      <c r="I32" s="130"/>
+      <c r="J32" s="130"/>
+      <c r="K32" s="130"/>
+      <c r="L32" s="130"/>
+      <c r="M32" s="130"/>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
+      <c r="A33" s="130"/>
+      <c r="B33" s="130"/>
+      <c r="C33" s="130"/>
+      <c r="D33" s="130"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="130"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="130"/>
+      <c r="L33" s="130"/>
+      <c r="M33" s="130"/>
     </row>
     <row r="34" spans="1:13" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
+      <c r="A34" s="130"/>
+      <c r="B34" s="130"/>
+      <c r="C34" s="130"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
+      <c r="J34" s="130"/>
+      <c r="K34" s="130"/>
+      <c r="L34" s="130"/>
+      <c r="M34" s="130"/>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="B35" s="131" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="132"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="132"/>
-      <c r="G35" s="132"/>
-      <c r="H35" s="132"/>
-      <c r="I35" s="132"/>
-      <c r="J35" s="133"/>
+      <c r="B35" s="54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="55"/>
+      <c r="D35" s="55"/>
+      <c r="E35" s="55"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="55"/>
+      <c r="H35" s="55"/>
+      <c r="I35" s="55"/>
+      <c r="J35" s="56"/>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
     </row>
     <row r="36" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
-      <c r="B36" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" s="134"/>
-      <c r="I36" s="135"/>
-      <c r="J36" s="139"/>
+      <c r="B36" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="138"/>
+      <c r="D36" s="139"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="58"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="63"/>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
     </row>
     <row r="37" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="136" t="s">
-        <v>44</v>
-      </c>
-      <c r="H37" s="137"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="140"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="142"/>
+      <c r="E37" s="143"/>
+      <c r="F37" s="144"/>
+      <c r="G37" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="61"/>
+      <c r="I37" s="62"/>
+      <c r="J37" s="64"/>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
     </row>
     <row r="38" spans="1:13" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
-      <c r="B38" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C38" s="36"/>
+      <c r="B38" s="81" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="82"/>
       <c r="D38" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="41"/>
+      <c r="E38" s="126" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="101"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="103"/>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
     </row>
     <row r="39" spans="1:13" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11"/>
-      <c r="B39" s="141" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" s="142"/>
-      <c r="D39" s="116"/>
-      <c r="E39" s="116"/>
-      <c r="F39" s="116"/>
-      <c r="G39" s="116"/>
-      <c r="H39" s="142"/>
-      <c r="I39" s="142"/>
-      <c r="J39" s="143"/>
+      <c r="B39" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="66"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="68"/>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
     </row>
     <row r="40" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
-      <c r="B40" s="123" t="s">
+      <c r="B40" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="37"/>
+      <c r="D40" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="41"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="124"/>
-      <c r="D40" s="102" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="125"/>
-      <c r="F40" s="125"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="107" t="s">
-        <v>53</v>
-      </c>
-      <c r="I40" s="111"/>
-      <c r="J40" s="108"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="45"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
     <row r="41" spans="1:13" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11"/>
-      <c r="B41" s="100"/>
-      <c r="C41" s="101"/>
-      <c r="D41" s="126" t="s">
-        <v>54</v>
-      </c>
-      <c r="E41" s="127"/>
-      <c r="F41" s="126" t="s">
-        <v>55</v>
-      </c>
-      <c r="G41" s="127"/>
-      <c r="H41" s="109"/>
-      <c r="I41" s="112"/>
-      <c r="J41" s="110"/>
+      <c r="B41" s="38"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="50"/>
+      <c r="F41" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="50"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="47"/>
+      <c r="J41" s="48"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
     <row r="42" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
-      <c r="B42" s="85" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="86"/>
-      <c r="D42" s="80"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="128"/>
-      <c r="I42" s="129"/>
-      <c r="J42" s="130"/>
+      <c r="B42" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="53"/>
       <c r="K42" s="15"/>
       <c r="L42" s="15"/>
       <c r="M42" s="15"/>
     </row>
     <row r="43" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
-      <c r="B43" s="85" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="86"/>
-      <c r="D43" s="80"/>
-      <c r="E43" s="81"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="82"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="84"/>
+      <c r="B43" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="145"/>
+      <c r="G43" s="146"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="28"/>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
     </row>
     <row r="44" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15"/>
-      <c r="B44" s="85" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" s="86"/>
-      <c r="D44" s="80"/>
-      <c r="E44" s="81"/>
-      <c r="F44" s="80"/>
-      <c r="G44" s="81"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="84"/>
+      <c r="B44" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="28"/>
       <c r="K44" s="15"/>
       <c r="L44" s="15"/>
       <c r="M44" s="15"/>
     </row>
     <row r="45" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15"/>
-      <c r="B45" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="28"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="118"/>
-      <c r="G45" s="119"/>
-      <c r="H45" s="120"/>
-      <c r="I45" s="121"/>
-      <c r="J45" s="122"/>
+      <c r="B45" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="79"/>
+      <c r="J45" s="80"/>
       <c r="K45" s="15"/>
       <c r="L45" s="15"/>
       <c r="M45" s="15"/>
     </row>
     <row r="46" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="15"/>
-      <c r="B46" s="85" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="86"/>
-      <c r="D46" s="80"/>
-      <c r="E46" s="81"/>
-      <c r="F46" s="80"/>
-      <c r="G46" s="81"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="105"/>
-      <c r="J46" s="106"/>
+      <c r="B46" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="18"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="23"/>
       <c r="K46" s="15"/>
       <c r="L46" s="15"/>
       <c r="M46" s="15"/>
     </row>
     <row r="47" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15"/>
-      <c r="B47" s="85" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="86"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="81"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="81"/>
-      <c r="H47" s="82"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="84"/>
+      <c r="B47" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="18"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="28"/>
       <c r="K47" s="15"/>
       <c r="L47" s="15"/>
       <c r="M47" s="15"/>
     </row>
     <row r="48" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
-      <c r="B48" s="85" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="86"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="81"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="81"/>
-      <c r="H48" s="82"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="84"/>
+      <c r="B48" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="18"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="28"/>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
     </row>
     <row r="49" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="15"/>
-      <c r="B49" s="144" t="s">
-        <v>62</v>
-      </c>
-      <c r="C49" s="145"/>
-      <c r="D49" s="146"/>
-      <c r="E49" s="147"/>
-      <c r="F49" s="146"/>
-      <c r="G49" s="147"/>
-      <c r="H49" s="148"/>
-      <c r="I49" s="149"/>
-      <c r="J49" s="150"/>
+      <c r="B49" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" s="30"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="35"/>
       <c r="K49" s="15"/>
       <c r="L49" s="15"/>
       <c r="M49" s="15"/>
     </row>
     <row r="50" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15"/>
-      <c r="B50" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="C50" s="116"/>
-      <c r="D50" s="116"/>
-      <c r="E50" s="116"/>
-      <c r="F50" s="116"/>
-      <c r="G50" s="116"/>
-      <c r="H50" s="116"/>
-      <c r="I50" s="116"/>
-      <c r="J50" s="117"/>
+      <c r="B50" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="67"/>
+      <c r="J50" s="75"/>
       <c r="K50" s="15"/>
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="15"/>
-      <c r="B51" s="107" t="s">
+      <c r="B51" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51" s="45"/>
+      <c r="D51" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" s="70"/>
+      <c r="F51" s="70"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="108"/>
-      <c r="D51" s="77" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="78"/>
-      <c r="F51" s="78"/>
-      <c r="G51" s="79"/>
-      <c r="H51" s="107" t="s">
-        <v>53</v>
-      </c>
-      <c r="I51" s="111"/>
-      <c r="J51" s="108"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="45"/>
       <c r="K51" s="15"/>
       <c r="L51" s="15"/>
       <c r="M51" s="15"/>
     </row>
     <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15"/>
-      <c r="B52" s="109"/>
-      <c r="C52" s="110"/>
-      <c r="D52" s="113" t="s">
-        <v>54</v>
-      </c>
-      <c r="E52" s="114"/>
-      <c r="F52" s="113" t="s">
-        <v>55</v>
-      </c>
-      <c r="G52" s="114"/>
-      <c r="H52" s="109"/>
-      <c r="I52" s="112"/>
-      <c r="J52" s="110"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="72" t="s">
+        <v>52</v>
+      </c>
+      <c r="E52" s="73"/>
+      <c r="F52" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="G52" s="73"/>
+      <c r="H52" s="46"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="48"/>
       <c r="K52" s="15"/>
       <c r="L52" s="15"/>
       <c r="M52" s="15"/>
     </row>
     <row r="53" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
-      <c r="B53" s="85" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" s="86"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105"/>
-      <c r="J53" s="106"/>
+      <c r="B53" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="18"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="23"/>
       <c r="K53" s="15"/>
       <c r="L53" s="15"/>
       <c r="M53" s="15"/>
     </row>
     <row r="54" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="15"/>
-      <c r="B54" s="85" t="s">
-        <v>65</v>
-      </c>
-      <c r="C54" s="86"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="81"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105"/>
-      <c r="J54" s="106"/>
+      <c r="B54" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="18"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="23"/>
       <c r="K54" s="15"/>
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
     </row>
     <row r="55" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="15"/>
-      <c r="B55" s="85" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="86"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="81"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="81"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105"/>
-      <c r="J55" s="106"/>
+      <c r="B55" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="18"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="23"/>
       <c r="K55" s="15"/>
       <c r="L55" s="15"/>
       <c r="M55" s="15"/>
     </row>
     <row r="56" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15"/>
-      <c r="B56" s="85" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="86"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="81"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="81"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105"/>
-      <c r="J56" s="106"/>
+      <c r="B56" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="18"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="22"/>
+      <c r="J56" s="23"/>
       <c r="K56" s="15"/>
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
     </row>
     <row r="57" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="15"/>
-      <c r="B57" s="85" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="86"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="81"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="81"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105"/>
-      <c r="J57" s="106"/>
+      <c r="B57" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="18"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="23"/>
       <c r="K57" s="15"/>
       <c r="L57" s="15"/>
       <c r="M57" s="15"/>
@@ -2779,7 +2762,7 @@
     <row r="59" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="11"/>
@@ -2787,30 +2770,30 @@
     </row>
     <row r="60" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
+      <c r="B60" s="135"/>
+      <c r="C60" s="135"/>
+      <c r="D60" s="135"/>
+      <c r="E60" s="135"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="135"/>
+      <c r="H60" s="135"/>
+      <c r="I60" s="135"/>
+      <c r="J60" s="135"/>
       <c r="K60" s="11"/>
       <c r="L60" s="11"/>
       <c r="M60" s="11"/>
     </row>
     <row r="61" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
+      <c r="B61" s="136"/>
+      <c r="C61" s="136"/>
+      <c r="D61" s="136"/>
+      <c r="E61" s="136"/>
+      <c r="F61" s="136"/>
+      <c r="G61" s="136"/>
+      <c r="H61" s="136"/>
+      <c r="I61" s="136"/>
+      <c r="J61" s="136"/>
       <c r="K61" s="11"/>
       <c r="L61" s="11"/>
       <c r="M61" s="11"/>
@@ -2818,7 +2801,7 @@
     <row r="62" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K62" s="11"/>
       <c r="L62" s="11"/>
@@ -2826,17 +2809,17 @@
     </row>
     <row r="63" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
-      <c r="B63" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="24"/>
-      <c r="J63" s="24"/>
+      <c r="B63" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" s="137"/>
+      <c r="D63" s="137"/>
+      <c r="E63" s="137"/>
+      <c r="F63" s="137"/>
+      <c r="G63" s="137"/>
+      <c r="H63" s="137"/>
+      <c r="I63" s="137"/>
+      <c r="J63" s="137"/>
       <c r="K63" s="11"/>
       <c r="L63" s="11"/>
       <c r="M63" s="11"/>
@@ -2844,7 +2827,7 @@
     <row r="64" spans="1:13" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="11"/>
       <c r="B64" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K64" s="11"/>
       <c r="L64" s="11"/>
@@ -2852,17 +2835,17 @@
     </row>
     <row r="65" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
-      <c r="B65" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
+      <c r="B65" s="135" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="135"/>
+      <c r="D65" s="135"/>
+      <c r="E65" s="135"/>
+      <c r="F65" s="135"/>
+      <c r="G65" s="135"/>
+      <c r="H65" s="135"/>
+      <c r="I65" s="135"/>
+      <c r="J65" s="135"/>
       <c r="K65" s="11"/>
       <c r="L65" s="11"/>
       <c r="M65" s="11"/>
@@ -2883,96 +2866,94 @@
       <c r="M66" s="11"/>
     </row>
     <row r="67" spans="1:13" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="47"/>
-      <c r="B67" s="47"/>
-      <c r="C67" s="47"/>
-      <c r="D67" s="47"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="45"/>
-      <c r="K67" s="47"/>
-      <c r="L67" s="47"/>
-      <c r="M67" s="47"/>
+      <c r="A67" s="150"/>
+      <c r="B67" s="150"/>
+      <c r="C67" s="150"/>
+      <c r="D67" s="150"/>
+      <c r="E67" s="148"/>
+      <c r="F67" s="148"/>
+      <c r="G67" s="150"/>
+      <c r="H67" s="150"/>
+      <c r="I67" s="148"/>
+      <c r="J67" s="148"/>
+      <c r="K67" s="150"/>
+      <c r="L67" s="150"/>
+      <c r="M67" s="150"/>
     </row>
     <row r="68" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="47"/>
-      <c r="B68" s="47"/>
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="45"/>
-      <c r="K68" s="47"/>
-      <c r="L68" s="47"/>
-      <c r="M68" s="47"/>
+      <c r="A68" s="150"/>
+      <c r="B68" s="150"/>
+      <c r="C68" s="150"/>
+      <c r="D68" s="150"/>
+      <c r="E68" s="148"/>
+      <c r="F68" s="148"/>
+      <c r="G68" s="150"/>
+      <c r="H68" s="150"/>
+      <c r="I68" s="148"/>
+      <c r="J68" s="148"/>
+      <c r="K68" s="150"/>
+      <c r="L68" s="150"/>
+      <c r="M68" s="150"/>
     </row>
     <row r="69" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="47"/>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="47"/>
-      <c r="I69" s="45"/>
-      <c r="J69" s="45"/>
-      <c r="K69" s="47"/>
-      <c r="L69" s="47"/>
-      <c r="M69" s="47"/>
+      <c r="A69" s="150"/>
+      <c r="B69" s="150"/>
+      <c r="C69" s="150"/>
+      <c r="D69" s="150"/>
+      <c r="E69" s="148"/>
+      <c r="F69" s="148"/>
+      <c r="G69" s="150"/>
+      <c r="H69" s="150"/>
+      <c r="I69" s="148"/>
+      <c r="J69" s="148"/>
+      <c r="K69" s="150"/>
+      <c r="L69" s="150"/>
+      <c r="M69" s="150"/>
     </row>
     <row r="70" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="47"/>
-      <c r="B70" s="47"/>
-      <c r="C70" s="47"/>
-      <c r="D70" s="47"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="47"/>
-      <c r="I70" s="45"/>
-      <c r="J70" s="45"/>
-      <c r="K70" s="47"/>
-      <c r="L70" s="47"/>
-      <c r="M70" s="47"/>
+      <c r="A70" s="150"/>
+      <c r="B70" s="150"/>
+      <c r="C70" s="150"/>
+      <c r="D70" s="150"/>
+      <c r="E70" s="148"/>
+      <c r="F70" s="148"/>
+      <c r="G70" s="150"/>
+      <c r="H70" s="150"/>
+      <c r="I70" s="148"/>
+      <c r="J70" s="148"/>
+      <c r="K70" s="150"/>
+      <c r="L70" s="150"/>
+      <c r="M70" s="150"/>
     </row>
     <row r="71" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="48"/>
-      <c r="B71" s="48"/>
-      <c r="C71" s="48"/>
-      <c r="D71" s="48"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="45"/>
-      <c r="J71" s="45"/>
-      <c r="K71" s="48"/>
-      <c r="L71" s="48"/>
-      <c r="M71" s="48"/>
+      <c r="A71" s="151"/>
+      <c r="B71" s="151"/>
+      <c r="C71" s="151"/>
+      <c r="D71" s="151"/>
+      <c r="E71" s="148"/>
+      <c r="F71" s="148"/>
+      <c r="G71" s="151"/>
+      <c r="H71" s="151"/>
+      <c r="I71" s="148"/>
+      <c r="J71" s="148"/>
+      <c r="K71" s="151"/>
+      <c r="L71" s="151"/>
+      <c r="M71" s="151"/>
     </row>
     <row r="72" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="44"/>
-      <c r="B72" s="44"/>
-      <c r="C72" s="44"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="H72" s="46"/>
-      <c r="I72" s="45"/>
-      <c r="J72" s="45"/>
-      <c r="K72" s="44"/>
-      <c r="L72" s="44"/>
-      <c r="M72" s="44"/>
+      <c r="A72" s="147"/>
+      <c r="B72" s="147"/>
+      <c r="C72" s="147"/>
+      <c r="D72" s="147"/>
+      <c r="E72" s="148"/>
+      <c r="F72" s="148"/>
+      <c r="G72" s="149"/>
+      <c r="H72" s="149"/>
+      <c r="I72" s="148"/>
+      <c r="J72" s="148"/>
+      <c r="K72" s="147"/>
+      <c r="L72" s="147"/>
+      <c r="M72" s="147"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="12"/>
@@ -2990,40 +2971,29 @@
       <c r="M73" s="12"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="18"/>
-      <c r="L74" s="18"/>
-      <c r="M74" s="18"/>
+      <c r="A74" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="131"/>
+      <c r="C74" s="131"/>
+      <c r="D74" s="131"/>
+      <c r="E74" s="131"/>
+      <c r="F74" s="131"/>
+      <c r="G74" s="131"/>
+      <c r="H74" s="131"/>
+      <c r="I74" s="131"/>
+      <c r="J74" s="131"/>
+      <c r="K74" s="131"/>
+      <c r="L74" s="131"/>
+      <c r="M74" s="131"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="151"/>
-      <c r="B75" s="151"/>
-      <c r="C75" s="151"/>
-      <c r="D75" s="151"/>
-      <c r="E75" s="151"/>
-      <c r="F75" s="152" t="s">
-        <v>46</v>
-      </c>
-      <c r="G75" s="152"/>
-      <c r="H75" s="151"/>
-      <c r="I75" s="151"/>
-      <c r="J75" s="151"/>
-      <c r="K75" s="151"/>
-      <c r="L75" s="151"/>
-      <c r="M75" s="151"/>
-    </row>
-    <row r="76" spans="1:13" s="151" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="F75" s="129" t="s">
+        <v>44</v>
+      </c>
+      <c r="G75" s="129"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25"/>
     <row r="84" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="88" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3033,6 +3003,140 @@
     <row r="106" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="158">
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="A32:M34"/>
+    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="B60:J61"/>
+    <mergeCell ref="B63:J63"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="D36:F37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="K72:M72"/>
+    <mergeCell ref="A67:D71"/>
+    <mergeCell ref="E67:F71"/>
+    <mergeCell ref="G67:H71"/>
+    <mergeCell ref="I67:J71"/>
+    <mergeCell ref="K67:M71"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="C3:M3"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="E8:M8"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="E9:M9"/>
+    <mergeCell ref="E10:M10"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E26:M26"/>
+    <mergeCell ref="E27:M27"/>
+    <mergeCell ref="E28:M28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="E15:M15"/>
+    <mergeCell ref="E16:M16"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E11:M11"/>
+    <mergeCell ref="E12:M12"/>
+    <mergeCell ref="E13:M13"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="B51:C52"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="H51:J52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="B50:J50"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:J41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="F42:G42"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="F57:G57"/>
@@ -3057,164 +3161,30 @@
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="F47:G47"/>
-    <mergeCell ref="B40:C41"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="H40:J41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="B51:C52"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="H51:J52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="B50:J50"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="A8:A16"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E14:M14"/>
-    <mergeCell ref="E15:M15"/>
-    <mergeCell ref="E16:M16"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E11:M11"/>
-    <mergeCell ref="E12:M12"/>
-    <mergeCell ref="E13:M13"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="E8:M8"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="E9:M9"/>
-    <mergeCell ref="E10:M10"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="E27:M27"/>
-    <mergeCell ref="E28:M28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="A32:M34"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="B60:J61"/>
-    <mergeCell ref="B63:J63"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="B36:C37"/>
-    <mergeCell ref="D36:F37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="K72:M72"/>
-    <mergeCell ref="A67:D71"/>
-    <mergeCell ref="E67:F71"/>
-    <mergeCell ref="G67:H71"/>
-    <mergeCell ref="I67:J71"/>
-    <mergeCell ref="K67:M71"/>
   </mergeCells>
   <conditionalFormatting sqref="A72:D72 K72:M72">
-    <cfRule type="containsBlanks" dxfId="5" priority="2">
+    <cfRule type="containsBlanks" dxfId="4" priority="2">
       <formula>LEN(TRIM(A72))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A72:D72">
-    <cfRule type="containsBlanks" dxfId="4" priority="4">
+    <cfRule type="containsBlanks" dxfId="3" priority="4">
       <formula>LEN(TRIM(A72))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D36:F37 J36:J37">
+    <cfRule type="containsBlanks" dxfId="2" priority="1">
+      <formula>LEN(TRIM(D36))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I4:M4 C5:H5 K5:M5 J7:M7 E8:M16 E20:M31">
-    <cfRule type="containsBlanks" dxfId="2" priority="7">
+    <cfRule type="containsBlanks" dxfId="1" priority="7">
       <formula>LEN(TRIM(C4))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K72:M72">
-    <cfRule type="containsBlanks" dxfId="1" priority="3">
+    <cfRule type="containsBlanks" dxfId="0" priority="3">
       <formula>LEN(TRIM(K72))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36:F37 J36:J37">
-    <cfRule type="containsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(D36))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="46">
